--- a/144/DQ Templates and Instructions/Topic 7 DQ 1/Topic 7 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 7 DQ 1/Topic 7 DQ 1.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{6A4D99AA-E2B2-4AEE-97DA-75E68C8FB365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{281033A8-A39B-45D5-A0FE-9D1AE4BF4459}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{6A4D99AA-E2B2-4AEE-97DA-75E68C8FB365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FB581FB-D997-4E14-9CCB-2372D794F7AE}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="270" windowWidth="23250" windowHeight="15555" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="3" r:id="rId1"/>
@@ -31,6 +31,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={366E1BCD-93BA-433D-9EC0-F17213977A6C}</author>
+  </authors>
+  <commentList>
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{366E1BCD-93BA-433D-9EC0-F17213977A6C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://youtu.be/H1qURI-xGtU</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
   <si>
@@ -262,7 +280,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +364,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1441,6 +1465,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="11" borderId="61" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1468,21 +1532,135 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1521,160 +1699,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="11" borderId="61" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2089,6 +2113,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="I13" dT="2026-07-16T20:21:41.63" personId="{00000000-0000-0000-0000-000000000000}" id="{366E1BCD-93BA-433D-9EC0-F17213977A6C}">
+    <text>https://youtu.be/H1qURI-xGtU</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>303181015</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="28" url="https://youtu.be/H1qURI-xGtU"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BCA7DD9-C1F4-45C8-9252-7A38951342B1}">
   <dimension ref="B3:I13"/>
@@ -2101,58 +2139,58 @@
       <c r="B3" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="63"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="77"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="66"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="80"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="66"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="66"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="80"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="69"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="83"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="60"/>
@@ -2189,7 +2227,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A419531-17DC-44AB-831A-B98ADE995472}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A419531-17DC-44AB-831A-B98ADE995472}">
   <dimension ref="A1:T28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2211,51 +2249,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="92"/>
-      <c r="N1" s="99" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="97"/>
+      <c r="N1" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="100"/>
+      <c r="O1" s="106"/>
     </row>
     <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="95"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="100"/>
       <c r="N2" s="40" t="s">
         <v>11</v>
       </c>
       <c r="O2" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
+      <c r="S2" s="90"/>
+      <c r="T2" s="90"/>
     </row>
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="95"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="100"/>
       <c r="N3" s="42" t="s">
         <v>13</v>
       </c>
@@ -2266,15 +2304,15 @@
       <c r="T3" s="4"/>
     </row>
     <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="95"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="100"/>
       <c r="N4" s="44" t="s">
         <v>15</v>
       </c>
@@ -2285,15 +2323,15 @@
       <c r="T4" s="4"/>
     </row>
     <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="93"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="95"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="100"/>
       <c r="N5" s="45" t="s">
         <v>17</v>
       </c>
@@ -2304,15 +2342,15 @@
       <c r="T5" s="4"/>
     </row>
     <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="93"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="95"/>
+      <c r="A6" s="98"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="100"/>
       <c r="N6" s="46" t="s">
         <v>19</v>
       </c>
@@ -2323,77 +2361,77 @@
       <c r="T6" s="4"/>
     </row>
     <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="93"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="95"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="100"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
     </row>
     <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="93"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="95"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="100"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
     <row r="9" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="93"/>
-      <c r="B9" s="115"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="115"/>
-      <c r="F9" s="115"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="95"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="100"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
     </row>
     <row r="10" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="116" t="s">
+      <c r="A10" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="118"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="86"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="105" t="s">
+      <c r="I10" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="106"/>
-      <c r="K10" s="107"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="111"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
     </row>
     <row r="11" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="103"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="111"/>
-      <c r="K11" s="122"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="114"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
     </row>
@@ -2404,26 +2442,26 @@
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="109"/>
-      <c r="K12" s="110"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="117"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
     </row>
     <row r="13" spans="1:20" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="101" t="s">
+      <c r="A13" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="98"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="104"/>
       <c r="F13" s="56"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="123" t="s">
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="118" t="s">
         <v>22</v>
       </c>
       <c r="J13" s="119"/>
@@ -2432,37 +2470,37 @@
       <c r="T13" s="4"/>
     </row>
     <row r="14" spans="1:20" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="126"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="128" t="s">
+      <c r="A14" s="93"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="128" t="s">
+      <c r="D14" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="128" t="s">
+      <c r="E14" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="128" t="s">
+      <c r="F14" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="128" t="s">
+      <c r="G14" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="128" t="s">
+      <c r="H14" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="129" t="s">
+      <c r="I14" s="67" t="s">
         <v>30</v>
       </c>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
     </row>
     <row r="15" spans="1:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="74"/>
+      <c r="B15" s="124"/>
       <c r="C15" s="48"/>
       <c r="D15" s="49"/>
       <c r="E15" s="49"/>
@@ -2473,26 +2511,26 @@
       <c r="H15" s="18">
         <v>5</v>
       </c>
-      <c r="I15" s="131"/>
+      <c r="I15" s="68"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
     </row>
     <row r="16" spans="1:20" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="132" t="s">
+      <c r="A16" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="136">
+      <c r="B16" s="126"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="71">
         <v>200</v>
       </c>
-      <c r="G16" s="137"/>
-      <c r="H16" s="138">
+      <c r="G16" s="72"/>
+      <c r="H16" s="73">
         <v>10</v>
       </c>
-      <c r="I16" s="139"/>
+      <c r="I16" s="74"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
     </row>
@@ -2504,77 +2542,77 @@
       <c r="E17" s="56"/>
       <c r="F17" s="1"/>
       <c r="G17" s="56"/>
-      <c r="H17" s="124" t="s">
+      <c r="H17" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="I17" s="125"/>
+      <c r="I17" s="65"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
     </row>
     <row r="18" spans="1:20" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="82"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="84"/>
+      <c r="B18" s="134"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="136"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
     </row>
     <row r="19" spans="1:20" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="85"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="84"/>
+      <c r="A19" s="137"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="136"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="85"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="84"/>
+      <c r="A20" s="137"/>
+      <c r="B20" s="135"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="136"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="84"/>
+      <c r="A21" s="137"/>
+      <c r="B21" s="135"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="136"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="87"/>
+      <c r="A22" s="137"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="139"/>
     </row>
     <row r="23" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75"/>
-      <c r="B23" s="76"/>
+      <c r="A23" s="127"/>
+      <c r="B23" s="128"/>
       <c r="C23" s="25" t="s">
         <v>35</v>
       </c>
@@ -2617,10 +2655,10 @@
       </c>
     </row>
     <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="129" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="78"/>
+      <c r="B24" s="130"/>
       <c r="C24" s="19">
         <f>D15</f>
         <v>0</v>
@@ -2663,10 +2701,10 @@
       <c r="Q24" s="15"/>
     </row>
     <row r="25" spans="1:20" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="79" t="s">
+      <c r="A25" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="80"/>
+      <c r="B25" s="132"/>
       <c r="C25" s="7"/>
       <c r="D25" s="20">
         <f t="shared" ref="D25:D28" si="0">$E$15</f>
@@ -2697,10 +2735,10 @@
       <c r="Q25" s="15"/>
     </row>
     <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="70" t="s">
+      <c r="A26" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="71"/>
+      <c r="B26" s="92"/>
       <c r="C26" s="7"/>
       <c r="D26" s="20">
         <f t="shared" si="0"/>
@@ -2731,10 +2769,10 @@
       <c r="Q26" s="15"/>
     </row>
     <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="71"/>
+      <c r="B27" s="92"/>
       <c r="C27" s="7"/>
       <c r="D27" s="20">
         <f t="shared" si="0"/>
@@ -2765,10 +2803,10 @@
       <c r="Q27" s="15"/>
     </row>
     <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="73"/>
+      <c r="B28" s="122"/>
       <c r="C28" s="8"/>
       <c r="D28" s="23">
         <f t="shared" si="0"/>
@@ -2800,6 +2838,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A18:I22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="S2:T2"/>
@@ -2811,14 +2857,6 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="I10:K12"/>
     <mergeCell ref="I13:K13"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A18:I22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A11" r:id="rId1" display="https://www.nyse.com/listings_directory/stock" xr:uid="{054FF35B-9775-4D9F-8365-DD27279E04C3}"/>
@@ -2827,17 +2865,17 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3058,15 +3096,43 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1108A294-D891-4423-BAC6-610CB4026109}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D789E95B-A6E1-432B-8794-BAC76EE7895F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+    <ds:schemaRef ds:uri="18557d39-01b8-4d71-9479-3fad465290ae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F89DC360-9B75-4BA6-93DD-980857BEB979}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3074,16 +3140,4 @@
     <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D789E95B-A6E1-432B-8794-BAC76EE7895F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1108A294-D891-4423-BAC6-610CB4026109}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>